--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N118_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N118_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.23135195430815</v>
+        <v>6.862594692575075</v>
       </c>
       <c r="D2" t="n">
-        <v>34.68292924658366</v>
+        <v>5.635976002569845</v>
       </c>
       <c r="E2" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F2" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.14706021746154</v>
+        <v>7.4988972853375</v>
       </c>
       <c r="D3" t="n">
-        <v>18.28557523486625</v>
+        <v>2.971405975665766</v>
       </c>
       <c r="E3" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F3" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.58913651282203</v>
+        <v>8.058234683333581</v>
       </c>
       <c r="D4" t="n">
-        <v>24.57130488943592</v>
+        <v>3.992837044533337</v>
       </c>
       <c r="E4" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F4" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.69738157360435</v>
+        <v>7.100824505710707</v>
       </c>
       <c r="D5" t="n">
-        <v>9.704450743553533</v>
+        <v>1.576973245827449</v>
       </c>
       <c r="E5" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F5" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.94734638947453</v>
+        <v>6.166443788289611</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6416738382672</v>
+        <v>5.954271998718419</v>
       </c>
       <c r="E6" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F6" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.1710075351682</v>
+        <v>5.715288724464833</v>
       </c>
       <c r="D7" t="n">
-        <v>7.685948225918025</v>
+        <v>1.248966586711679</v>
       </c>
       <c r="E7" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F7" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.26619068393853</v>
+        <v>3.943255986140011</v>
       </c>
       <c r="D8" t="n">
-        <v>24.74020410184711</v>
+        <v>4.020283166550156</v>
       </c>
       <c r="E8" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F8" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.95489088843372</v>
+        <v>7.142669769370479</v>
       </c>
       <c r="D9" t="n">
-        <v>48.32584281070845</v>
+        <v>7.852949456740124</v>
       </c>
       <c r="E9" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F9" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>11.05666792993046</v>
+        <v>1.7967085386137</v>
       </c>
       <c r="D10" t="n">
-        <v>11.07726100734389</v>
+        <v>1.800054913693383</v>
       </c>
       <c r="E10" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F10" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.56604585615312</v>
+        <v>5.616982451624882</v>
       </c>
       <c r="D11" t="n">
-        <v>36.17015735455103</v>
+        <v>5.877650570114542</v>
       </c>
       <c r="E11" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F11" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.87554652072473</v>
+        <v>3.554776309617769</v>
       </c>
       <c r="D12" t="n">
-        <v>21.48405881248367</v>
+        <v>3.491159557028597</v>
       </c>
       <c r="E12" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F12" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.77515708790043</v>
+        <v>5.16346302678382</v>
       </c>
       <c r="D13" t="n">
-        <v>31.80419735697797</v>
+        <v>5.16818207050892</v>
       </c>
       <c r="E13" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F13" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>7.07031983794843</v>
+        <v>1.14892697366662</v>
       </c>
       <c r="D14" t="n">
-        <v>10.69167561735897</v>
+        <v>1.737397287820833</v>
       </c>
       <c r="E14" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F14" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>48.61253725209705</v>
+        <v>7.89953730346577</v>
       </c>
       <c r="D15" t="n">
-        <v>43.02292146826508</v>
+        <v>6.991224738593076</v>
       </c>
       <c r="E15" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F15" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>8.647020370590125</v>
+        <v>1.405140810220895</v>
       </c>
       <c r="D16" t="n">
-        <v>4.863516565583572</v>
+        <v>0.7903214419073304</v>
       </c>
       <c r="E16" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F16" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>20.23001483979237</v>
+        <v>3.28737741146626</v>
       </c>
       <c r="D17" t="n">
-        <v>14.79930430700583</v>
+        <v>2.404886949888447</v>
       </c>
       <c r="E17" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F17" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>14.58997436660666</v>
+        <v>2.370870834573583</v>
       </c>
       <c r="D18" t="n">
-        <v>14.66983952686011</v>
+        <v>2.383848923114768</v>
       </c>
       <c r="E18" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F18" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>40.8327730098128</v>
+        <v>6.635325614094581</v>
       </c>
       <c r="D19" t="n">
-        <v>34.71462272523071</v>
+        <v>5.641126192849991</v>
       </c>
       <c r="E19" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F19" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>27.07159008067602</v>
+        <v>4.399133388109853</v>
       </c>
       <c r="D20" t="n">
-        <v>21.00279353210422</v>
+        <v>3.412953948966936</v>
       </c>
       <c r="E20" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F20" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>21.78685306572866</v>
+        <v>3.540363623180907</v>
       </c>
       <c r="D21" t="n">
-        <v>23.93363219437909</v>
+        <v>3.889215231586602</v>
       </c>
       <c r="E21" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F21" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>23.86903954352463</v>
+        <v>3.878718925822753</v>
       </c>
       <c r="D22" t="n">
-        <v>20.1368238572116</v>
+        <v>3.272233876796886</v>
       </c>
       <c r="E22" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F22" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>59.85472949624495</v>
+        <v>9.726393543139805</v>
       </c>
       <c r="D23" t="n">
-        <v>56.17117003736444</v>
+        <v>9.127815131071722</v>
       </c>
       <c r="E23" t="n">
-        <v>14.26409579538602</v>
+        <v>2.317915566750229</v>
       </c>
       <c r="F23" t="n">
-        <v>13.45408066943052</v>
+        <v>2.186288108782461</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
